--- a/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,292 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01J6RM7PH3DX54S93ABHZ8J2X8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K3TMT9CQB86XXAZ9FY9M1QYW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K3TMW0YGBNCAV57V69WX0VWV</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01JPHQ5NVAN9KMV1ZDAFZBR9CH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Integration Features</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>User Life Cycle</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#01K4A9WTC4984KJ3X6ABQ5B8WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Match Expression</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KR0JN5BMWTANVCFG91BND6AD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0JN5BMWTANVCFG91BND6AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Manage Create Conditions</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KR0K4Q8SHRN3XQT8XSCDSY61</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0K4Q8SHRN3XQT8XSCDSY61</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Manage Update Conditions</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KR0KKRGFR3S392A1PXCSW7ZM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0KKRGFR3S392A1PXCSW7ZM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Manage Termination conditions</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KR0KRSXPH65MG7JGHQD4CE15</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0KRSXPH65MG7JGHQD4CE15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Contact Life cycle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KR0M2Y0BWTBK7PGFX56QXPMQ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0M2Y0BWTBK7PGFX56QXPMQ</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,6 +746,72 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KR0VBSP51DD0N03WFD89GDZY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0VBSP51DD0N03WFD89GDZY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Notification Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KR0WVB8FVEYW8RMW77QWF7RY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0WVB8FVEYW8RMW77QWF7RY</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,28 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,6 +834,72 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Log Insight Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KR13ZJP93G2W9JPJ4DWC8523</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR13ZJP93G2W9JPJ4DWC8523</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KR1CENX2E7NKJ7GDVEBB5QK1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR1CENX2E7NKJ7GDVEBB5QK1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>User Life Cycle</t>
+          <t>User Lifecycle Management</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Create Conditions</t>
+          <t>Manage Creation Conditions</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Termination conditions</t>
+          <t>Manage Termination Conditions</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Contact Life cycle</t>
+          <t>Contact Lifecycle Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,95 +749,95 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Match Condition for Contact Creations and Updates</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KR0VBSP51DD0N03WFD89GDZY</t>
+          <t>h_01KRAWGCTHPSVZ5MM7H92R7CSS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0VBSP51DD0N03WFD89GDZY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRAWGCTHPSVZ5MM7H92R7CSS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Match Condition for Certinia Users and Contacts</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>h_01KRB2QZX4Z6VMJA0TVJYNBCN4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB2QZX4Z6VMJA0TVJYNBCN4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Manage Contact Creation Conditions</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KR0WVB8FVEYW8RMW77QWF7RY</t>
+          <t>h_01KRB2QZX4PXTWPF0MCHSR8FYN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0WVB8FVEYW8RMW77QWF7RY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB2QZX4PXTWPF0MCHSR8FYN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Manage Contact Update Conditions</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KRB2QZX41ETHTN5RTGW4B8V7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB2QZX41ETHTN5RTGW4B8V7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Debug Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,54 +847,142 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KR13ZJP93G2W9JPJ4DWC8523</t>
+          <t>h_01KR0VBSP51DD0N03WFD89GDZY</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR13ZJP93G2W9JPJ4DWC8523</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0VBSP51DD0N03WFD89GDZY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KR0WVB8FVEYW8RMW77QWF7RY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR0WVB8FVEYW8RMW77QWF7RY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Insights Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KR13ZJP93G2W9JPJ4DWC8523</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR13ZJP93G2W9JPJ4DWC8523</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Schedule</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>h_01KR1CENX2E7NKJ7GDVEBB5QK1</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KR1CENX2E7NKJ7GDVEBB5QK1</t>
         </is>

--- a/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
+++ b/site/Certinia-Entra-ID-Integration-Guide/headings.xlsx
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Manage Creation Conditions</t>
+          <t>Manage Creation Condition</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Update Conditions</t>
+          <t>Manage Update Condition</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Termination Conditions</t>
+          <t>Manage Termination Condition</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KRB2QZX4Z6VMJA0TVJYNBCN4</t>
+          <t>h_01KRB3VDZGFH6ZMKEAJP80FRDE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB2QZX4Z6VMJA0TVJYNBCN4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB3VDZGFH6ZMKEAJP80FRDE</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KRB2QZX4PXTWPF0MCHSR8FYN</t>
+          <t>h_01KRB3VDZG0JA9EHK01J1D8W9P</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB2QZX4PXTWPF0MCHSR8FYN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB3VDZG0JA9EHK01J1D8W9P</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KRB2QZX41ETHTN5RTGW4B8V7</t>
+          <t>h_01KRB3VDZGGXHBN6NZ9N9F6F5Z</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB2QZX41ETHTN5RTGW4B8V7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Certinia-Entra-ID-Integration-Guide/#h_01KRB3VDZGGXHBN6NZ9N9F6F5Z</t>
         </is>
       </c>
     </row>
